--- a/evals/unit_tests_comparative/test03_attention_fused_vs_unfused/analysis_output_ref/perf_report_trace1.xlsx
+++ b/evals/unit_tests_comparative/test03_attention_fused_vs_unfused/analysis_output_ref/perf_report_trace1.xlsx
@@ -11,8 +11,9 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="diff_stats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="unified_perf_callstacks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="diff_stats" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,311 +972,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>process_name</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>process_label</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>thread_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Input Dims</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Input type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Input Strides</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ex_UID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>operation_count</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>total_duration_us</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>mean_duration_us</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>std_duration_us</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_mean</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_std</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>speedup (trace2/trace1)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>delta_us (trace2 - trace1)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>lca_kernel_count_trace2</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>lca_id</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>lca_name</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>lca_total_kernel_time_trace1_us</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>lca_total_kernel_time_trace2_us</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_median</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_min</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_max</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_median</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_min</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_max</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>kernel_details_summary</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>trunc_kernel_details</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>perf_params</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>has_perf_model</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Cumulative Percentage (%)</t>
+          <t>call_stack</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>aiter::_flash_attn_forward</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>SDPA_fwd</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>((8, 512, 16, 64), (8, 512, 16, 64), (8, 512, 16, 64))</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>('c10::bfloat16', 'c10::bfloat16', 'c10::bfloat16')</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>30</v>
-      </c>
-      <c r="M2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>350</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>350</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.228571428571429</v>
-      </c>
-      <c r="S2" t="n">
-        <v>430</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>attention</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>350</v>
-      </c>
-      <c r="X2" t="n">
-        <v>780</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>350</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>350</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>350</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t&gt;&gt;', 'stream': 0, 'gpu_op_uid': 6, 'count': 1, 'total_duration_us': np.float64(350.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(350.0), 'median_duration_us': np.float64(350.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(350.0), 'max_duration_us': np.float64(350.0)}]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128,...', 'stream': 0, 'mean_duration_us': np.float64(350.0)}]</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>100</v>
+          <t>aiter::_flash_attn_forward =&gt; aiter::_flash_attn_forward</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1289,6 +1028,334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AK2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>op category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>process_label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Input type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ex_UID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>operation_count</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>total_duration_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mean_duration_us</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>std_duration_us</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>speedup (trace2/trace1)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>delta_us (trace2 - trace1)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>lca_count_trace2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>lca_id</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>lca_name</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lca_total_kernel_time_trace1_us</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>lca_total_kernel_time_trace2_us</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_median</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_min</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_max</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details_summary</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>perf_params</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>has_perf_model</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_call_stack</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative Percentage (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aiter::_flash_attn_forward</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SDPA_fwd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>((8, 512, 16, 64), (8, 512, 16, 64), (8, 512, 16, 64))</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>('c10::bfloat16', 'c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>350</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>350</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.228571428571429</v>
+      </c>
+      <c r="S2" t="n">
+        <v>430</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>attention</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>350</v>
+      </c>
+      <c r="X2" t="n">
+        <v>780</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t&gt;&gt;', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(350.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(350.0), 'median_duration_us': np.float64(350.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(350.0), 'max_duration_us': np.float64(350.0)}]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128,...', 'stream': 0, 'mean_duration_us': np.float64(350.0)}]</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>aiter::_flash_attn_forward =&gt; aiter::_flash_attn_forward</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
